--- a/questionnaire_templates/030_writing_group_interest_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/030_writing_group_interest_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>writing_group_interest_survey_page_1</t>
+          <t>intro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -528,7 +528,11 @@
           <t>Introduction</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Welcome to this Writing Group Interest Survey.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,20 +542,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>writing_group_interest_survey_page_2</t>
+          <t>about_you_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>About You</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is your primary role in the group?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please select one of the options below.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>writing_group_interest_survey_page_3</t>
+          <t>about_you_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>About You (continued)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What brings you here?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide a brief explanation.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>what_brings_you_here</t>
+          <t>writing_group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what brings you here</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What type of writing group are you interested in?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>writing_group_interest_survey_page_4</t>
+          <t>writing_group_preferences</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Writing Group</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What type of writing group settings would you like?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>writing_group_interest_survey_page_5</t>
+          <t>writing_group_schedules</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Writing Group (continued)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What schedule would you like for your writing group?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>writing_group_interest_survey_page_6</t>
+          <t>about_me</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Writing Group (continued)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>About You</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please provide a brief description.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>writing_group_interest_survey_page_7</t>
+          <t>what_we_can_do</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Writing Group (continued)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What would you like to achieve or gain in the group?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>writing_group_interest_survey_page_8</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Writing Group (continued)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please provide any other comments or thoughts.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,361 +763,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>writing_group_interest_survey_page_9</t>
+          <t>thank_you</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Writing Group (continued)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Thank You</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>We value your time and participation.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>writing_group_interest_survey_page_10</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Writing Group (continued)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>writing_group_interest_survey_page_11</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Writing Group (continued)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>writing_group_interest_survey_page_12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Writing Group (continued)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>writing_group_interest_survey_page_13</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Writing Group (continued)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>writing_group_interest_survey_page_14</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Writing Group (continued)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>writing_group_interest_survey_page_15</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Writing Group (continued)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>writing_group_interest_survey_page_16</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Writing Group (continued)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>writing_group_interest_survey_page_17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Writing Group (continued)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>writing_group_interest_survey_page_18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Writing Group (continued)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>what_brings_you_here_continued</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>what brings you here (continued)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>writing_group_interest_survey_page_19</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Additional Comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>writing_group_interest_survey_page_20</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Thank You</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>writing_group_interest_survey_page_21</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Thank You (continued)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>writing_group_interest_survey_page_22</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Thank You (continued)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>writing_group_interest_survey_page_23</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Thank You (continued)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +793,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,34 +821,340 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>writing_group_interest_survey_page_4_choices</t>
+          <t>about_you_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>i_am_a_writer/author</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>I am a writer/author</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>writing_group_interest_survey_page_4_choices</t>
+          <t>about_you_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>i_am_an_editor/publisher</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>I am an editor/publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>about_you_1_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>i_am_a_reader/fan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>I am a reader/fan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>about_you_1_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>writing_group_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>creative_writing_group</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Creative Writing Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>writing_group_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>non-fiction_writing_group</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Non-Fiction Writing Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>writing_group_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>poetry_group</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Poetry Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>writing_group_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>playwriting_group</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Playwriting Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>writing_group_preferences_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>writing_group_preferences_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>in-person</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>writing_group_preferences_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>writing_group_preferences_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>flexible/remote</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Flexible/remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>writing_group_schedules_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>writing_group_schedules_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>bi-weekly</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bi-weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>writing_group_schedules_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>writing_group_schedules_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Flexible</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>what_we_can_do_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>feedback</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>what_we_can_do_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>networking</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>what_we_can_do_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>community</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>what_we_can_do_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>professional_growth</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Professional growth</t>
         </is>
       </c>
     </row>
